--- a/data/DIM_TAM.xlsx
+++ b/data/DIM_TAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://freightways-my.sharepoint.com/personal/tuan_nguyen_dxmail_co_nz/Documents/Desktop/DXMail Master/Project/Sales Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb76a992d3c9d4c0/Desktop/Sales Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E936FC32-DFA0-4BA0-874E-F3AA6094169F}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_F25DC773A252ABDACC1048F1995C62D85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D28019-5300-4BB3-91C1-843A720ED8C1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,19 +30,19 @@
     <t>ID</t>
   </si>
   <si>
+    <t>REP1</t>
+  </si>
+  <si>
+    <t>REP2</t>
+  </si>
+  <si>
+    <t>REP3</t>
+  </si>
+  <si>
+    <t>REP4</t>
+  </si>
+  <si>
     <t>TAM</t>
-  </si>
-  <si>
-    <t>TAM1</t>
-  </si>
-  <si>
-    <t>TAM2</t>
-  </si>
-  <si>
-    <t>TAM3</t>
-  </si>
-  <si>
-    <t>TAM4</t>
   </si>
 </sst>
 </file>
@@ -101,6 +101,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -378,46 +382,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
